--- a/Data/Rules/Wild Meadow Farms Rules Matrix.xlsx
+++ b/Data/Rules/Wild Meadow Farms Rules Matrix.xlsx
@@ -760,37 +760,37 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H2" t="b">
         <v>0</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K2" t="b">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N2" t="b">
         <v>0</v>
       </c>
       <c r="O2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q2" t="b">
         <v>0</v>
@@ -808,52 +808,52 @@
         <v>2</v>
       </c>
       <c r="V2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W2" t="b">
         <v>0</v>
       </c>
       <c r="X2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Z2" t="b">
         <v>0</v>
       </c>
       <c r="AA2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC2" t="b">
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AF2" t="b">
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AI2" t="b">
         <v>0</v>
       </c>
       <c r="AJ2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AK2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AL2" t="b">
         <v>1</v>
@@ -865,7 +865,7 @@
         <v>0</v>
       </c>
       <c r="AO2">
-        <v>37</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:41">
@@ -885,37 +885,37 @@
         <v>0</v>
       </c>
       <c r="F3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H3" t="b">
         <v>0</v>
       </c>
       <c r="I3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K3" t="b">
         <v>0</v>
       </c>
       <c r="L3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N3" t="b">
         <v>0</v>
       </c>
       <c r="O3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q3" t="b">
         <v>0</v>
@@ -930,28 +930,28 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W3" t="b">
         <v>0</v>
       </c>
       <c r="X3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Z3" t="b">
         <v>0</v>
       </c>
       <c r="AA3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AC3" t="b">
         <v>0</v>
@@ -966,19 +966,19 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AI3" t="b">
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AK3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AL3" t="b">
         <v>1</v>
@@ -990,7 +990,7 @@
         <v>0</v>
       </c>
       <c r="AO3">
-        <v>37</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:41">
@@ -1010,19 +1010,19 @@
         <v>0</v>
       </c>
       <c r="F4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H4" t="b">
         <v>0</v>
       </c>
       <c r="I4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K4" t="b">
         <v>0</v>
@@ -1037,73 +1037,73 @@
         <v>0</v>
       </c>
       <c r="O4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q4" t="b">
         <v>0</v>
       </c>
       <c r="R4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T4" t="b">
         <v>0</v>
       </c>
       <c r="U4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="W4" t="b">
         <v>0</v>
       </c>
       <c r="X4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Z4" t="b">
         <v>0</v>
       </c>
       <c r="AA4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC4" t="b">
         <v>0</v>
       </c>
       <c r="AD4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AF4" t="b">
         <v>0</v>
       </c>
       <c r="AG4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AI4" t="b">
         <v>0</v>
       </c>
       <c r="AJ4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AK4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AL4" t="b">
         <v>1</v>
@@ -1115,7 +1115,7 @@
         <v>0</v>
       </c>
       <c r="AO4">
-        <v>37</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:41">
@@ -1135,100 +1135,100 @@
         <v>0</v>
       </c>
       <c r="F5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H5" t="b">
         <v>0</v>
       </c>
       <c r="I5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K5" t="b">
         <v>0</v>
       </c>
       <c r="L5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N5" t="b">
         <v>0</v>
       </c>
       <c r="O5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q5" t="b">
         <v>0</v>
       </c>
       <c r="R5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T5" t="b">
         <v>0</v>
       </c>
       <c r="U5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="W5" t="b">
         <v>0</v>
       </c>
       <c r="X5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Z5" t="b">
         <v>0</v>
       </c>
       <c r="AA5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AC5" t="b">
         <v>0</v>
       </c>
       <c r="AD5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AF5" t="b">
         <v>0</v>
       </c>
       <c r="AG5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AI5" t="b">
         <v>0</v>
       </c>
       <c r="AJ5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AK5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AL5" t="b">
         <v>1</v>
@@ -1240,7 +1240,7 @@
         <v>0</v>
       </c>
       <c r="AO5">
-        <v>37</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:41">
@@ -1269,91 +1269,91 @@
         <v>0</v>
       </c>
       <c r="I6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K6" t="b">
         <v>0</v>
       </c>
       <c r="L6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N6" t="b">
         <v>0</v>
       </c>
       <c r="O6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q6" t="b">
         <v>0</v>
       </c>
       <c r="R6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T6" t="b">
         <v>0</v>
       </c>
       <c r="U6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W6" t="b">
         <v>0</v>
       </c>
       <c r="X6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Z6" t="b">
         <v>0</v>
       </c>
       <c r="AA6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC6" t="b">
         <v>0</v>
       </c>
       <c r="AD6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AF6" t="b">
         <v>0</v>
       </c>
       <c r="AG6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AI6" t="b">
         <v>0</v>
       </c>
       <c r="AJ6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AK6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AL6" t="b">
         <v>1</v>
@@ -1365,7 +1365,7 @@
         <v>0</v>
       </c>
       <c r="AO6">
-        <v>37</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:41">
@@ -1394,28 +1394,28 @@
         <v>0</v>
       </c>
       <c r="I7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K7" t="b">
         <v>0</v>
       </c>
       <c r="L7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M7">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N7" t="b">
         <v>0</v>
       </c>
       <c r="O7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q7" t="b">
         <v>0</v>
@@ -1439,46 +1439,46 @@
         <v>0</v>
       </c>
       <c r="X7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y7">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Z7" t="b">
         <v>0</v>
       </c>
       <c r="AA7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AC7" t="b">
         <v>0</v>
       </c>
       <c r="AD7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AF7" t="b">
         <v>0</v>
       </c>
       <c r="AG7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH7">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AI7" t="b">
         <v>0</v>
       </c>
       <c r="AJ7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AK7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AL7" t="b">
         <v>1</v>
@@ -1490,7 +1490,7 @@
         <v>0</v>
       </c>
       <c r="AO7">
-        <v>37</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:41">
@@ -1510,37 +1510,37 @@
         <v>0</v>
       </c>
       <c r="F8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G8">
+        <v>2</v>
+      </c>
+      <c r="H8" t="b">
+        <v>0</v>
+      </c>
+      <c r="I8">
         <v>3</v>
       </c>
-      <c r="H8" t="b">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>2</v>
-      </c>
       <c r="J8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K8" t="b">
         <v>0</v>
       </c>
       <c r="L8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N8" t="b">
         <v>0</v>
       </c>
       <c r="O8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q8" t="b">
         <v>0</v>
@@ -1558,52 +1558,52 @@
         <v>2</v>
       </c>
       <c r="V8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W8" t="b">
         <v>0</v>
       </c>
       <c r="X8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Z8" t="b">
         <v>0</v>
       </c>
       <c r="AA8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AC8" t="b">
         <v>0</v>
       </c>
       <c r="AD8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AF8" t="b">
         <v>0</v>
       </c>
       <c r="AG8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH8">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AI8" t="b">
         <v>0</v>
       </c>
       <c r="AJ8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AK8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AL8" t="b">
         <v>1</v>
@@ -1615,7 +1615,7 @@
         <v>0</v>
       </c>
       <c r="AO8">
-        <v>37</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:41">
@@ -1635,88 +1635,88 @@
         <v>0</v>
       </c>
       <c r="F9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G9">
+        <v>2</v>
+      </c>
+      <c r="H9" t="b">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>1</v>
+      </c>
+      <c r="J9">
+        <v>1</v>
+      </c>
+      <c r="K9" t="b">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>1</v>
+      </c>
+      <c r="M9">
+        <v>1</v>
+      </c>
+      <c r="N9" t="b">
+        <v>0</v>
+      </c>
+      <c r="O9">
+        <v>1</v>
+      </c>
+      <c r="P9">
+        <v>1</v>
+      </c>
+      <c r="Q9" t="b">
+        <v>0</v>
+      </c>
+      <c r="R9">
+        <v>1</v>
+      </c>
+      <c r="S9">
+        <v>1</v>
+      </c>
+      <c r="T9" t="b">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>1</v>
+      </c>
+      <c r="V9">
+        <v>2</v>
+      </c>
+      <c r="W9" t="b">
+        <v>0</v>
+      </c>
+      <c r="X9">
+        <v>1</v>
+      </c>
+      <c r="Y9">
+        <v>1</v>
+      </c>
+      <c r="Z9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA9">
+        <v>1</v>
+      </c>
+      <c r="AB9">
+        <v>1</v>
+      </c>
+      <c r="AC9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD9">
+        <v>1</v>
+      </c>
+      <c r="AE9">
+        <v>1</v>
+      </c>
+      <c r="AF9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9">
         <v>3</v>
-      </c>
-      <c r="H9" t="b">
-        <v>0</v>
-      </c>
-      <c r="I9">
-        <v>2</v>
-      </c>
-      <c r="J9">
-        <v>3</v>
-      </c>
-      <c r="K9" t="b">
-        <v>0</v>
-      </c>
-      <c r="L9">
-        <v>2</v>
-      </c>
-      <c r="M9">
-        <v>4</v>
-      </c>
-      <c r="N9" t="b">
-        <v>0</v>
-      </c>
-      <c r="O9">
-        <v>2</v>
-      </c>
-      <c r="P9">
-        <v>3</v>
-      </c>
-      <c r="Q9" t="b">
-        <v>0</v>
-      </c>
-      <c r="R9">
-        <v>2</v>
-      </c>
-      <c r="S9">
-        <v>3</v>
-      </c>
-      <c r="T9" t="b">
-        <v>0</v>
-      </c>
-      <c r="U9">
-        <v>2</v>
-      </c>
-      <c r="V9">
-        <v>4</v>
-      </c>
-      <c r="W9" t="b">
-        <v>0</v>
-      </c>
-      <c r="X9">
-        <v>2</v>
-      </c>
-      <c r="Y9">
-        <v>4</v>
-      </c>
-      <c r="Z9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA9">
-        <v>2</v>
-      </c>
-      <c r="AB9">
-        <v>3</v>
-      </c>
-      <c r="AC9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD9">
-        <v>2</v>
-      </c>
-      <c r="AE9">
-        <v>3</v>
-      </c>
-      <c r="AF9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG9">
-        <v>2</v>
       </c>
       <c r="AH9">
         <v>4</v>
@@ -1725,10 +1725,10 @@
         <v>0</v>
       </c>
       <c r="AJ9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AK9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AL9" t="b">
         <v>1</v>
@@ -1740,7 +1740,7 @@
         <v>0</v>
       </c>
       <c r="AO9">
-        <v>37</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:41">
@@ -1760,10 +1760,10 @@
         <v>0</v>
       </c>
       <c r="F10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H10" t="b">
         <v>0</v>
@@ -1778,82 +1778,82 @@
         <v>0</v>
       </c>
       <c r="L10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M10">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N10" t="b">
         <v>0</v>
       </c>
       <c r="O10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q10" t="b">
         <v>0</v>
       </c>
       <c r="R10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T10" t="b">
         <v>0</v>
       </c>
       <c r="U10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W10" t="b">
         <v>0</v>
       </c>
       <c r="X10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y10">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Z10" t="b">
         <v>0</v>
       </c>
       <c r="AA10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AC10" t="b">
         <v>0</v>
       </c>
       <c r="AD10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AF10" t="b">
         <v>0</v>
       </c>
       <c r="AG10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH10">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AI10" t="b">
         <v>0</v>
       </c>
       <c r="AJ10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AK10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AL10" t="b">
         <v>1</v>
@@ -1865,7 +1865,7 @@
         <v>0</v>
       </c>
       <c r="AO10">
-        <v>37</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:41">
@@ -1885,19 +1885,19 @@
         <v>0</v>
       </c>
       <c r="F11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H11" t="b">
         <v>0</v>
       </c>
       <c r="I11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K11" t="b">
         <v>0</v>
@@ -1912,10 +1912,10 @@
         <v>0</v>
       </c>
       <c r="O11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q11" t="b">
         <v>0</v>
@@ -1930,19 +1930,19 @@
         <v>0</v>
       </c>
       <c r="U11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V11">
+        <v>2</v>
+      </c>
+      <c r="W11" t="b">
+        <v>0</v>
+      </c>
+      <c r="X11">
         <v>4</v>
       </c>
-      <c r="W11" t="b">
-        <v>0</v>
-      </c>
-      <c r="X11">
-        <v>2</v>
-      </c>
       <c r="Y11">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Z11" t="b">
         <v>0</v>
@@ -1969,16 +1969,16 @@
         <v>2</v>
       </c>
       <c r="AH11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI11" t="b">
         <v>0</v>
       </c>
       <c r="AJ11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AK11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AL11" t="b">
         <v>1</v>
@@ -1990,7 +1990,7 @@
         <v>0</v>
       </c>
       <c r="AO11">
-        <v>37</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12" spans="1:41">
@@ -2010,10 +2010,10 @@
         <v>0</v>
       </c>
       <c r="F12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G12">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H12" t="b">
         <v>0</v>
@@ -2037,46 +2037,46 @@
         <v>0</v>
       </c>
       <c r="O12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P12">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q12" t="b">
         <v>0</v>
       </c>
       <c r="R12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S12">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T12" t="b">
         <v>0</v>
       </c>
       <c r="U12">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="V12">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="W12" t="b">
         <v>0</v>
       </c>
       <c r="X12">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Y12">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Z12" t="b">
         <v>0</v>
       </c>
       <c r="AA12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB12">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AC12" t="b">
         <v>0</v>
@@ -2091,19 +2091,19 @@
         <v>0</v>
       </c>
       <c r="AG12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH12">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AI12" t="b">
         <v>0</v>
       </c>
       <c r="AJ12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AK12">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AL12" t="b">
         <v>1</v>
@@ -2115,7 +2115,7 @@
         <v>0</v>
       </c>
       <c r="AO12">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:41">
@@ -2135,19 +2135,19 @@
         <v>0</v>
       </c>
       <c r="F13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H13" t="b">
         <v>0</v>
       </c>
       <c r="I13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K13" t="b">
         <v>0</v>
@@ -2162,46 +2162,46 @@
         <v>0</v>
       </c>
       <c r="O13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P13">
+        <v>2</v>
+      </c>
+      <c r="Q13" t="b">
+        <v>0</v>
+      </c>
+      <c r="R13">
+        <v>1</v>
+      </c>
+      <c r="S13">
+        <v>1</v>
+      </c>
+      <c r="T13" t="b">
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <v>2</v>
+      </c>
+      <c r="V13">
         <v>3</v>
       </c>
-      <c r="Q13" t="b">
-        <v>0</v>
-      </c>
-      <c r="R13">
-        <v>2</v>
-      </c>
-      <c r="S13">
-        <v>3</v>
-      </c>
-      <c r="T13" t="b">
-        <v>0</v>
-      </c>
-      <c r="U13">
-        <v>2</v>
-      </c>
-      <c r="V13">
-        <v>4</v>
-      </c>
       <c r="W13" t="b">
         <v>0</v>
       </c>
       <c r="X13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y13">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Z13" t="b">
         <v>0</v>
       </c>
       <c r="AA13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AC13" t="b">
         <v>0</v>
@@ -2219,16 +2219,16 @@
         <v>2</v>
       </c>
       <c r="AH13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI13" t="b">
         <v>0</v>
       </c>
       <c r="AJ13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AK13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AL13" t="b">
         <v>1</v>
@@ -2240,7 +2240,7 @@
         <v>0</v>
       </c>
       <c r="AO13">
-        <v>37</v>
+        <v>21</v>
       </c>
     </row>
     <row r="14" spans="1:41">
@@ -2260,100 +2260,100 @@
         <v>0</v>
       </c>
       <c r="F14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H14" t="b">
         <v>0</v>
       </c>
       <c r="I14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K14" t="b">
         <v>0</v>
       </c>
       <c r="L14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N14" t="b">
         <v>0</v>
       </c>
       <c r="O14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q14" t="b">
         <v>0</v>
       </c>
       <c r="R14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T14" t="b">
         <v>0</v>
       </c>
       <c r="U14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W14" t="b">
         <v>0</v>
       </c>
       <c r="X14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Z14" t="b">
         <v>0</v>
       </c>
       <c r="AA14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AC14" t="b">
         <v>0</v>
       </c>
       <c r="AD14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AF14" t="b">
         <v>0</v>
       </c>
       <c r="AG14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AI14" t="b">
         <v>0</v>
       </c>
       <c r="AJ14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AK14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AL14" t="b">
         <v>1</v>
@@ -2365,7 +2365,7 @@
         <v>0</v>
       </c>
       <c r="AO14">
-        <v>37</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:41">
@@ -2385,100 +2385,100 @@
         <v>0</v>
       </c>
       <c r="F15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H15" t="b">
         <v>0</v>
       </c>
       <c r="I15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K15" t="b">
         <v>0</v>
       </c>
       <c r="L15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M15">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N15" t="b">
         <v>0</v>
       </c>
       <c r="O15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q15" t="b">
         <v>0</v>
       </c>
       <c r="R15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T15" t="b">
         <v>0</v>
       </c>
       <c r="U15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V15">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="W15" t="b">
         <v>0</v>
       </c>
       <c r="X15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y15">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Z15" t="b">
         <v>0</v>
       </c>
       <c r="AA15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AC15" t="b">
         <v>0</v>
       </c>
       <c r="AD15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AF15" t="b">
         <v>0</v>
       </c>
       <c r="AG15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AI15" t="b">
         <v>0</v>
       </c>
       <c r="AJ15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AK15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AL15" t="b">
         <v>1</v>
@@ -2490,7 +2490,7 @@
         <v>0</v>
       </c>
       <c r="AO15">
-        <v>37</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:41">
@@ -2510,100 +2510,100 @@
         <v>0</v>
       </c>
       <c r="F16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G16">
+        <v>1</v>
+      </c>
+      <c r="H16" t="b">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>1</v>
+      </c>
+      <c r="J16">
+        <v>1</v>
+      </c>
+      <c r="K16" t="b">
+        <v>0</v>
+      </c>
+      <c r="L16">
+        <v>2</v>
+      </c>
+      <c r="M16">
         <v>3</v>
       </c>
-      <c r="H16" t="b">
-        <v>0</v>
-      </c>
-      <c r="I16">
-        <v>2</v>
-      </c>
-      <c r="J16">
-        <v>3</v>
-      </c>
-      <c r="K16" t="b">
-        <v>0</v>
-      </c>
-      <c r="L16">
-        <v>2</v>
-      </c>
-      <c r="M16">
-        <v>4</v>
-      </c>
       <c r="N16" t="b">
         <v>0</v>
       </c>
       <c r="O16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P16">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q16" t="b">
         <v>0</v>
       </c>
       <c r="R16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S16">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T16" t="b">
         <v>0</v>
       </c>
       <c r="U16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V16">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="W16" t="b">
         <v>0</v>
       </c>
       <c r="X16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y16">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Z16" t="b">
         <v>0</v>
       </c>
       <c r="AA16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB16">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AC16" t="b">
         <v>0</v>
       </c>
       <c r="AD16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE16">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AF16" t="b">
         <v>0</v>
       </c>
       <c r="AG16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH16">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AI16" t="b">
         <v>0</v>
       </c>
       <c r="AJ16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AK16">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AL16" t="b">
         <v>1</v>
@@ -2615,7 +2615,7 @@
         <v>0</v>
       </c>
       <c r="AO16">
-        <v>37</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17" spans="1:41">
@@ -2635,19 +2635,19 @@
         <v>0</v>
       </c>
       <c r="F17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G17">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H17" t="b">
         <v>0</v>
       </c>
       <c r="I17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J17">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K17" t="b">
         <v>0</v>
@@ -2662,37 +2662,37 @@
         <v>0</v>
       </c>
       <c r="O17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P17">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q17" t="b">
         <v>0</v>
       </c>
       <c r="R17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S17">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T17" t="b">
         <v>0</v>
       </c>
       <c r="U17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V17">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="W17" t="b">
         <v>0</v>
       </c>
       <c r="X17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y17">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Z17" t="b">
         <v>0</v>
@@ -2707,19 +2707,19 @@
         <v>0</v>
       </c>
       <c r="AD17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE17">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AF17" t="b">
         <v>0</v>
       </c>
       <c r="AG17">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AH17">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI17" t="b">
         <v>0</v>
@@ -2740,7 +2740,7 @@
         <v>0</v>
       </c>
       <c r="AO17">
-        <v>37</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18" spans="1:41">
@@ -2760,100 +2760,100 @@
         <v>0</v>
       </c>
       <c r="F18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G18">
+        <v>1</v>
+      </c>
+      <c r="H18" t="b">
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>1</v>
+      </c>
+      <c r="J18">
+        <v>1</v>
+      </c>
+      <c r="K18" t="b">
+        <v>0</v>
+      </c>
+      <c r="L18">
+        <v>2</v>
+      </c>
+      <c r="M18">
         <v>3</v>
       </c>
-      <c r="H18" t="b">
-        <v>0</v>
-      </c>
-      <c r="I18">
-        <v>2</v>
-      </c>
-      <c r="J18">
+      <c r="N18" t="b">
+        <v>0</v>
+      </c>
+      <c r="O18">
+        <v>1</v>
+      </c>
+      <c r="P18">
+        <v>1</v>
+      </c>
+      <c r="Q18" t="b">
+        <v>0</v>
+      </c>
+      <c r="R18">
+        <v>1</v>
+      </c>
+      <c r="S18">
+        <v>1</v>
+      </c>
+      <c r="T18" t="b">
+        <v>0</v>
+      </c>
+      <c r="U18">
+        <v>2</v>
+      </c>
+      <c r="V18">
         <v>3</v>
       </c>
-      <c r="K18" t="b">
-        <v>0</v>
-      </c>
-      <c r="L18">
-        <v>2</v>
-      </c>
-      <c r="M18">
-        <v>4</v>
-      </c>
-      <c r="N18" t="b">
-        <v>0</v>
-      </c>
-      <c r="O18">
-        <v>2</v>
-      </c>
-      <c r="P18">
-        <v>3</v>
-      </c>
-      <c r="Q18" t="b">
-        <v>0</v>
-      </c>
-      <c r="R18">
-        <v>2</v>
-      </c>
-      <c r="S18">
-        <v>3</v>
-      </c>
-      <c r="T18" t="b">
-        <v>0</v>
-      </c>
-      <c r="U18">
-        <v>2</v>
-      </c>
-      <c r="V18">
-        <v>4</v>
-      </c>
       <c r="W18" t="b">
         <v>0</v>
       </c>
       <c r="X18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y18">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Z18" t="b">
         <v>0</v>
       </c>
       <c r="AA18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB18">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AC18" t="b">
         <v>0</v>
       </c>
       <c r="AD18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE18">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AF18" t="b">
         <v>0</v>
       </c>
       <c r="AG18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH18">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AI18" t="b">
         <v>0</v>
       </c>
       <c r="AJ18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AK18">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AL18" t="b">
         <v>1</v>
@@ -2865,7 +2865,7 @@
         <v>0</v>
       </c>
       <c r="AO18">
-        <v>37</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19" spans="1:41">
@@ -2885,100 +2885,100 @@
         <v>0</v>
       </c>
       <c r="F19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G19">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H19" t="b">
         <v>0</v>
       </c>
       <c r="I19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J19">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K19" t="b">
         <v>0</v>
       </c>
       <c r="L19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M19">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N19" t="b">
         <v>0</v>
       </c>
       <c r="O19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P19">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q19" t="b">
         <v>0</v>
       </c>
       <c r="R19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S19">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T19" t="b">
         <v>0</v>
       </c>
       <c r="U19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V19">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="W19" t="b">
         <v>0</v>
       </c>
       <c r="X19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y19">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Z19" t="b">
         <v>0</v>
       </c>
       <c r="AA19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB19">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AC19" t="b">
         <v>0</v>
       </c>
       <c r="AD19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE19">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AF19" t="b">
         <v>0</v>
       </c>
       <c r="AG19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH19">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AI19" t="b">
         <v>0</v>
       </c>
       <c r="AJ19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AK19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AL19" t="b">
         <v>1</v>
@@ -2990,7 +2990,7 @@
         <v>0</v>
       </c>
       <c r="AO19">
-        <v>37</v>
+        <v>12</v>
       </c>
     </row>
     <row r="20" spans="1:41">
@@ -3010,28 +3010,28 @@
         <v>0</v>
       </c>
       <c r="F20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G20">
+        <v>1</v>
+      </c>
+      <c r="H20" t="b">
+        <v>0</v>
+      </c>
+      <c r="I20">
+        <v>1</v>
+      </c>
+      <c r="J20">
+        <v>1</v>
+      </c>
+      <c r="K20" t="b">
+        <v>0</v>
+      </c>
+      <c r="L20">
+        <v>2</v>
+      </c>
+      <c r="M20">
         <v>3</v>
-      </c>
-      <c r="H20" t="b">
-        <v>0</v>
-      </c>
-      <c r="I20">
-        <v>2</v>
-      </c>
-      <c r="J20">
-        <v>3</v>
-      </c>
-      <c r="K20" t="b">
-        <v>0</v>
-      </c>
-      <c r="L20">
-        <v>2</v>
-      </c>
-      <c r="M20">
-        <v>4</v>
       </c>
       <c r="N20" t="b">
         <v>0</v>
@@ -3046,64 +3046,64 @@
         <v>0</v>
       </c>
       <c r="R20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S20">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T20" t="b">
         <v>0</v>
       </c>
       <c r="U20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V20">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="W20" t="b">
         <v>0</v>
       </c>
       <c r="X20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y20">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Z20" t="b">
         <v>0</v>
       </c>
       <c r="AA20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB20">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AC20" t="b">
         <v>0</v>
       </c>
       <c r="AD20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE20">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AF20" t="b">
         <v>0</v>
       </c>
       <c r="AG20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH20">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AI20" t="b">
         <v>0</v>
       </c>
       <c r="AJ20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AK20">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AL20" t="b">
         <v>1</v>
@@ -3115,7 +3115,7 @@
         <v>0</v>
       </c>
       <c r="AO20">
-        <v>37</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21" spans="1:41">
@@ -3135,100 +3135,100 @@
         <v>0</v>
       </c>
       <c r="F21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G21">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H21" t="b">
         <v>0</v>
       </c>
       <c r="I21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J21">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K21" t="b">
         <v>0</v>
       </c>
       <c r="L21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M21">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N21" t="b">
         <v>0</v>
       </c>
       <c r="O21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P21">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q21" t="b">
         <v>0</v>
       </c>
       <c r="R21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S21">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T21" t="b">
         <v>0</v>
       </c>
       <c r="U21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V21">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W21" t="b">
         <v>0</v>
       </c>
       <c r="X21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y21">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Z21" t="b">
         <v>0</v>
       </c>
       <c r="AA21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB21">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AC21" t="b">
         <v>0</v>
       </c>
       <c r="AD21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE21">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AF21" t="b">
         <v>0</v>
       </c>
       <c r="AG21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH21">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AI21" t="b">
         <v>0</v>
       </c>
       <c r="AJ21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AK21">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AL21" t="b">
         <v>1</v>
@@ -3240,7 +3240,7 @@
         <v>0</v>
       </c>
       <c r="AO21">
-        <v>37</v>
+        <v>12</v>
       </c>
     </row>
     <row r="22" spans="1:41">
@@ -3260,100 +3260,100 @@
         <v>0</v>
       </c>
       <c r="F22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G22">
+        <v>2</v>
+      </c>
+      <c r="H22" t="b">
+        <v>0</v>
+      </c>
+      <c r="I22">
+        <v>1</v>
+      </c>
+      <c r="J22">
+        <v>1</v>
+      </c>
+      <c r="K22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L22">
+        <v>1</v>
+      </c>
+      <c r="M22">
+        <v>1</v>
+      </c>
+      <c r="N22" t="b">
+        <v>0</v>
+      </c>
+      <c r="O22">
+        <v>1</v>
+      </c>
+      <c r="P22">
+        <v>1</v>
+      </c>
+      <c r="Q22" t="b">
+        <v>0</v>
+      </c>
+      <c r="R22">
+        <v>1</v>
+      </c>
+      <c r="S22">
+        <v>1</v>
+      </c>
+      <c r="T22" t="b">
+        <v>0</v>
+      </c>
+      <c r="U22">
+        <v>1</v>
+      </c>
+      <c r="V22">
+        <v>1</v>
+      </c>
+      <c r="W22" t="b">
+        <v>0</v>
+      </c>
+      <c r="X22">
+        <v>1</v>
+      </c>
+      <c r="Y22">
+        <v>1</v>
+      </c>
+      <c r="Z22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA22">
+        <v>1</v>
+      </c>
+      <c r="AB22">
+        <v>1</v>
+      </c>
+      <c r="AC22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD22">
+        <v>1</v>
+      </c>
+      <c r="AE22">
+        <v>1</v>
+      </c>
+      <c r="AF22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22">
+        <v>2</v>
+      </c>
+      <c r="AH22">
         <v>3</v>
       </c>
-      <c r="H22" t="b">
-        <v>0</v>
-      </c>
-      <c r="I22">
-        <v>2</v>
-      </c>
-      <c r="J22">
-        <v>3</v>
-      </c>
-      <c r="K22" t="b">
-        <v>0</v>
-      </c>
-      <c r="L22">
-        <v>2</v>
-      </c>
-      <c r="M22">
-        <v>4</v>
-      </c>
-      <c r="N22" t="b">
-        <v>0</v>
-      </c>
-      <c r="O22">
-        <v>2</v>
-      </c>
-      <c r="P22">
-        <v>3</v>
-      </c>
-      <c r="Q22" t="b">
-        <v>0</v>
-      </c>
-      <c r="R22">
-        <v>2</v>
-      </c>
-      <c r="S22">
-        <v>3</v>
-      </c>
-      <c r="T22" t="b">
-        <v>0</v>
-      </c>
-      <c r="U22">
-        <v>2</v>
-      </c>
-      <c r="V22">
-        <v>4</v>
-      </c>
-      <c r="W22" t="b">
-        <v>0</v>
-      </c>
-      <c r="X22">
-        <v>2</v>
-      </c>
-      <c r="Y22">
-        <v>4</v>
-      </c>
-      <c r="Z22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA22">
-        <v>2</v>
-      </c>
-      <c r="AB22">
-        <v>3</v>
-      </c>
-      <c r="AC22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD22">
-        <v>2</v>
-      </c>
-      <c r="AE22">
-        <v>3</v>
-      </c>
-      <c r="AF22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG22">
-        <v>2</v>
-      </c>
-      <c r="AH22">
-        <v>4</v>
-      </c>
       <c r="AI22" t="b">
         <v>0</v>
       </c>
       <c r="AJ22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AK22">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AL22" t="b">
         <v>1</v>
@@ -3365,7 +3365,7 @@
         <v>0</v>
       </c>
       <c r="AO22">
-        <v>37</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23" spans="1:41">
@@ -3385,28 +3385,28 @@
         <v>0</v>
       </c>
       <c r="F23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G23">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H23" t="b">
         <v>0</v>
       </c>
       <c r="I23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K23" t="b">
         <v>0</v>
       </c>
       <c r="L23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M23">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N23" t="b">
         <v>0</v>
@@ -3421,52 +3421,52 @@
         <v>0</v>
       </c>
       <c r="R23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S23">
+        <v>1</v>
+      </c>
+      <c r="T23" t="b">
+        <v>0</v>
+      </c>
+      <c r="U23">
+        <v>1</v>
+      </c>
+      <c r="V23">
+        <v>1</v>
+      </c>
+      <c r="W23" t="b">
+        <v>0</v>
+      </c>
+      <c r="X23">
+        <v>1</v>
+      </c>
+      <c r="Y23">
+        <v>1</v>
+      </c>
+      <c r="Z23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA23">
+        <v>1</v>
+      </c>
+      <c r="AB23">
+        <v>1</v>
+      </c>
+      <c r="AC23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD23">
+        <v>1</v>
+      </c>
+      <c r="AE23">
+        <v>1</v>
+      </c>
+      <c r="AF23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23">
         <v>3</v>
-      </c>
-      <c r="T23" t="b">
-        <v>0</v>
-      </c>
-      <c r="U23">
-        <v>2</v>
-      </c>
-      <c r="V23">
-        <v>4</v>
-      </c>
-      <c r="W23" t="b">
-        <v>0</v>
-      </c>
-      <c r="X23">
-        <v>2</v>
-      </c>
-      <c r="Y23">
-        <v>4</v>
-      </c>
-      <c r="Z23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA23">
-        <v>2</v>
-      </c>
-      <c r="AB23">
-        <v>3</v>
-      </c>
-      <c r="AC23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD23">
-        <v>2</v>
-      </c>
-      <c r="AE23">
-        <v>3</v>
-      </c>
-      <c r="AF23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG23">
-        <v>2</v>
       </c>
       <c r="AH23">
         <v>4</v>
@@ -3475,10 +3475,10 @@
         <v>0</v>
       </c>
       <c r="AJ23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AK23">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AL23" t="b">
         <v>1</v>
@@ -3490,7 +3490,7 @@
         <v>0</v>
       </c>
       <c r="AO23">
-        <v>37</v>
+        <v>17</v>
       </c>
     </row>
     <row r="24" spans="1:41">
@@ -3510,100 +3510,100 @@
         <v>0</v>
       </c>
       <c r="F24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G24">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H24" t="b">
         <v>0</v>
       </c>
       <c r="I24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J24">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K24" t="b">
         <v>0</v>
       </c>
       <c r="L24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M24">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N24" t="b">
         <v>0</v>
       </c>
       <c r="O24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P24">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q24" t="b">
         <v>0</v>
       </c>
       <c r="R24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S24">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T24" t="b">
         <v>0</v>
       </c>
       <c r="U24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V24">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W24" t="b">
         <v>0</v>
       </c>
       <c r="X24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y24">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Z24" t="b">
         <v>0</v>
       </c>
       <c r="AA24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB24">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AC24" t="b">
         <v>0</v>
       </c>
       <c r="AD24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE24">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF24" t="b">
         <v>0</v>
       </c>
       <c r="AG24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH24">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AI24" t="b">
         <v>0</v>
       </c>
       <c r="AJ24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AK24">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AL24" t="b">
         <v>1</v>
@@ -3615,7 +3615,7 @@
         <v>0</v>
       </c>
       <c r="AO24">
-        <v>37</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25" spans="1:41">
@@ -3635,37 +3635,37 @@
         <v>0</v>
       </c>
       <c r="F25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G25">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H25" t="b">
         <v>0</v>
       </c>
       <c r="I25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J25">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K25" t="b">
         <v>0</v>
       </c>
       <c r="L25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M25">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N25" t="b">
         <v>0</v>
       </c>
       <c r="O25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P25">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q25" t="b">
         <v>0</v>
@@ -3680,55 +3680,55 @@
         <v>0</v>
       </c>
       <c r="U25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V25">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="W25" t="b">
         <v>0</v>
       </c>
       <c r="X25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y25">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Z25" t="b">
         <v>0</v>
       </c>
       <c r="AA25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB25">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AC25" t="b">
         <v>0</v>
       </c>
       <c r="AD25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE25">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AF25" t="b">
         <v>0</v>
       </c>
       <c r="AG25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH25">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AI25" t="b">
         <v>0</v>
       </c>
       <c r="AJ25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AK25">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AL25" t="b">
         <v>1</v>
@@ -3740,7 +3740,7 @@
         <v>0</v>
       </c>
       <c r="AO25">
-        <v>37</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
